--- a/base.xlsx
+++ b/base.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,25 +459,40 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>FEVEREIRO 2025</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MÉDIA 6M</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>MÉDIA 3M</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>META FEVEREIRO</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>R+C</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FORECAST SEMANA ANTERIOR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>FORECAST 02</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ESTOQUE</t>
         </is>
@@ -525,18 +540,27 @@
         </is>
       </c>
       <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>900</v>
+      </c>
+      <c r="K2" t="n">
+        <v>950</v>
+      </c>
+      <c r="L2" t="n">
         <v>1100</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>500</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>800</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>850</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -548,12 +572,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GER1</t>
+          <t>GER2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>COORD1</t>
+          <t>COORD2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -582,18 +606,27 @@
         </is>
       </c>
       <c r="I3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L3" t="n">
         <v>2100</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>900</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>1600</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>1700</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
